--- a/alerta.xlsx
+++ b/alerta.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>nome de célula</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>A GRAvE deseja-lhe boas férias!</t>
-  </si>
-  <si>
-    <t>A GRAvE deseja-lhe b</t>
   </si>
 </sst>
 </file>
@@ -640,7 +637,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>14</v>

--- a/alerta.xlsx
+++ b/alerta.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="EsteLivro" defaultThemeVersion="124226"/>
+  <workbookProtection workbookPassword="C98E" lockStructure="1"/>
   <bookViews>
     <workbookView showSheetTabs="0" xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540"/>
   </bookViews>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>nome de célula</t>
   </si>
@@ -334,6 +335,73 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>44450</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="[0]!EsteLivro.proteger" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectângulo 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10934700" y="38100"/>
+          <a:ext cx="508000" cy="133350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,7 +698,7 @@
     <col min="1" max="1" width="53.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.54296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="58.54296875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="19.90625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.6328125" style="4" customWidth="1"/>
     <col min="5" max="26" width="8.7265625" style="4"/>
     <col min="27" max="16384" width="8.7265625" style="1"/>
   </cols>
@@ -856,9 +924,7 @@
       <c r="D27" s="7"/>
     </row>
     <row r="28" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="A28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
     </row>
@@ -968,6 +1034,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
 

--- a/alerta.xlsx
+++ b/alerta.xlsx
@@ -130,16 +130,16 @@
     <t>https://graveex.wordpress.com/2019/09/14/primeiros-passos/</t>
   </si>
   <si>
-    <t>https://graveex.wordpress.com/2024/11/03/importacao-de-dados-pelo-inovar/</t>
-  </si>
-  <si>
-    <t>O AvInovar foi atualizado. Saiba mais aqui!</t>
-  </si>
-  <si>
     <t>smtp.sapo.pt</t>
   </si>
   <si>
-    <t>A GRAvE deseja-lhe boas férias!</t>
+    <t>A GRAvE deseja-lhe um boom ano letivo!</t>
+  </si>
+  <si>
+    <t>Veja as novidades da versão 44.</t>
+  </si>
+  <si>
+    <t>https://graveex.wordpress.com/2026/08/27/versao-44-disponivel/</t>
   </si>
 </sst>
 </file>
@@ -705,7 +705,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>14</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>30</v>
@@ -733,7 +733,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -744,7 +744,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
@@ -752,7 +752,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>32</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="20" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>25</v>

--- a/alerta.xlsx
+++ b/alerta.xlsx
@@ -133,13 +133,13 @@
     <t>smtp.sapo.pt</t>
   </si>
   <si>
-    <t>A GRAvE deseja-lhe um boom ano letivo!</t>
-  </si>
-  <si>
     <t>Veja as novidades da versão 44.</t>
   </si>
   <si>
     <t>https://graveex.wordpress.com/2026/08/27/versao-44-disponivel/</t>
+  </si>
+  <si>
+    <t>A GRAvE deseja-lhe um bom ano letivo!</t>
   </si>
 </sst>
 </file>
@@ -705,7 +705,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>14</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>30</v>
@@ -733,7 +733,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -744,7 +744,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>32</v>

--- a/alerta.xlsx
+++ b/alerta.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>nome de célula</t>
   </si>
@@ -133,13 +133,16 @@
     <t>smtp.sapo.pt</t>
   </si>
   <si>
-    <t>Veja as novidades da versão 44.</t>
-  </si>
-  <si>
-    <t>https://graveex.wordpress.com/2026/08/27/versao-44-disponivel/</t>
-  </si>
-  <si>
     <t>A GRAvE deseja-lhe um bom ano letivo!</t>
+  </si>
+  <si>
+    <t>https://graveex.wordpress.com/2026/09/17/correcao-da-grave-44/</t>
+  </si>
+  <si>
+    <t>Usa módulos? Abra a ligação.</t>
+  </si>
+  <si>
+    <t>Usa módulos?Clique aqui.</t>
   </si>
 </sst>
 </file>
@@ -705,7 +708,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>14</v>
@@ -722,7 +725,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>30</v>
@@ -732,14 +735,14 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
-        <v>39</v>
+      <c r="A4" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>35</v>
+      <c r="C4" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -752,7 +755,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -760,7 +763,7 @@
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>32</v>
@@ -1031,10 +1034,11 @@
     <hyperlink ref="A16" r:id="rId3"/>
     <hyperlink ref="A100" r:id="rId4"/>
     <hyperlink ref="A5" r:id="rId5" display="https://graveex.wordpress.com"/>
+    <hyperlink ref="C4" r:id="rId6" display="https://graveex.wordpress.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
 

--- a/alerta.xlsx
+++ b/alerta.xlsx
@@ -139,10 +139,10 @@
     <t>https://graveex.wordpress.com/2026/09/17/correcao-da-grave-44/</t>
   </si>
   <si>
-    <t>Usa módulos? Abra a ligação.</t>
-  </si>
-  <si>
-    <t>Usa módulos?Clique aqui.</t>
+    <t>Usa módulos? Clique aqui.</t>
+  </si>
+  <si>
+    <t>A GRAvE enviadas até 17 de setembro têm uma falha se usar módulos. Clique em sim para saber mais.</t>
   </si>
 </sst>
 </file>
@@ -736,7 +736,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>32</v>

--- a/alerta.xlsx
+++ b/alerta.xlsx
@@ -755,7 +755,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
